--- a/data/trans_dic/P21D_5_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,63</t>
+          <t>0,11; 1,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,33</t>
+          <t>0,12; 1,28</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,86</t>
+          <t>0,14; 0,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,44</t>
+          <t>0,08; 0,5</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,12</t>
+          <t>0,09; 1,23</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,52</t>
+          <t>0,06; 0,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,69</t>
+          <t>0,18; 0,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,48</t>
+          <t>0,15; 0,49</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5333</t>
+          <t>0; 5392</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>365; 5483</t>
+          <t>368; 5423</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>743; 7563</t>
+          <t>703; 7275</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3529</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1288; 8067</t>
+          <t>1271; 7785</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1595; 8972</t>
+          <t>1643; 10226</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5693</t>
+          <t>0; 6147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3306</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>573; 6958</t>
+          <t>573; 7640</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>979; 8657</t>
+          <t>1012; 9885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2771; 10979</t>
+          <t>2867; 11139</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4492; 15561</t>
+          <t>4798; 15838</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_5_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,61</t>
+          <t>0,11; 1,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,28</t>
+          <t>0,13; 1,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,4</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,83</t>
+          <t>0,17; 0,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,5</t>
+          <t>0,1; 0,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,23</t>
+          <t>0,09; 0,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,6</t>
+          <t>0,06; 0,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,7</t>
+          <t>0,2; 0,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,49</t>
+          <t>0,17; 0,5</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2893</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5392</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>368; 5423</t>
+          <t>388; 5748</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>703; 7275</t>
+          <t>802; 7584</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4748</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4414</t>
+          <t>0; 3262</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1271; 7785</t>
+          <t>1660; 8654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1643; 10226</t>
+          <t>1896; 9708</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2423</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6147</t>
+          <t>0; 7616</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>573; 7640</t>
+          <t>591; 6596</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1012; 9885</t>
+          <t>993; 8771</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2867; 11139</t>
+          <t>3306; 12529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4798; 15838</t>
+          <t>5632; 16318</t>
         </is>
       </c>
     </row>
